--- a/data/processed/rankings_frequencies.xlsx
+++ b/data/processed/rankings_frequencies.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C411"/>
+  <dimension ref="A1:C409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,27 +464,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inseguridad</t>
+          <t>salamanca</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01856763925729443</v>
+        <v>0.02652519893899204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>salamanco</t>
+          <t>inseguridad</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01193633952254642</v>
+        <v>0.01856763925729443</v>
       </c>
     </row>
     <row r="6">
@@ -516,20 +516,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>salamanca</t>
+          <t>visitar</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01061007957559682</v>
+        <v>0.009283819628647215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>visitar</t>
+          <t>malo</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -542,7 +542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>malo</t>
+          <t>turistico</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -555,7 +555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>turistico</t>
+          <t>variedad</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -568,20 +568,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>variedad</t>
+          <t>bonito</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009283819628647215</v>
+        <v>0.007957559681697613</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bonito</t>
+          <t>ver</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -594,7 +594,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>precio</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -607,7 +607,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>cosa</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -620,7 +620,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cosa</t>
+          <t>comida</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -633,20 +633,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>comida</t>
+          <t>gobierno</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007957559681697613</v>
+        <v>0.006631299734748011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gobierno</t>
+          <t>descuidado</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -659,7 +659,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>descuidado</t>
+          <t>cultura</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -672,7 +672,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cultura</t>
+          <t>zona</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -685,7 +685,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zona</t>
+          <t>persona</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -698,7 +698,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>persona</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -711,7 +711,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>salir</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -724,7 +724,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>salir</t>
+          <t>atractivo</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -737,7 +737,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>atractivo</t>
+          <t>peligroso</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -750,7 +750,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>peligroso</t>
+          <t>transporte</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -763,20 +763,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>transporte</t>
+          <t>gastronomia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006631299734748011</v>
+        <v>0.005305039787798408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gastronomia</t>
+          <t>actividad</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -789,7 +789,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>actividad</t>
+          <t>falta</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -802,7 +802,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>falta</t>
+          <t>seguridad</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -815,7 +815,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>seguridad</t>
+          <t>contaminacion</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -828,7 +828,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>contaminacion</t>
+          <t>poder</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -841,7 +841,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>poder</t>
+          <t>refineria</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -854,7 +854,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>refineria</t>
+          <t>ejemplo</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -867,7 +867,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ejemplo</t>
+          <t>tanto</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -880,7 +880,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tanto</t>
+          <t>aspecto</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -893,7 +893,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>aspecto</t>
+          <t>inseguro</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -906,7 +906,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>inseguro</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -919,7 +919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>calle</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -932,7 +932,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>calle</t>
+          <t>sentir</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -945,7 +945,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sentir</t>
+          <t>ofrecer</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -958,20 +958,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ofrecer</t>
+          <t>potencial</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>0.005305039787798408</v>
+        <v>0.003978779840848806</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>potencial</t>
+          <t>atracción</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -984,7 +984,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>atracción</t>
+          <t>gente</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -997,7 +997,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>salamancar</t>
+          <t>actualmente</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1010,7 +1010,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gente</t>
+          <t>vida</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1023,7 +1023,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>actualmente</t>
+          <t>ayudar</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1036,7 +1036,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>vida</t>
+          <t>feo</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1049,7 +1049,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ayudar</t>
+          <t>sucio</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1062,7 +1062,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>feo</t>
+          <t>mayoria</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1075,7 +1075,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sucio</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1088,7 +1088,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mayoria</t>
+          <t>amigo</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1101,7 +1101,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>familiar</t>
+          <t>tema</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1114,7 +1114,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>amigo</t>
+          <t>contaminado</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1127,7 +1127,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tema</t>
+          <t>restaurante</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1140,7 +1140,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>contaminado</t>
+          <t>q</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1153,7 +1153,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>restaurante</t>
+          <t>mantenimiento</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1166,7 +1166,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1179,7 +1179,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>considerar</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1192,7 +1192,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1205,33 +1205,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>considerar</t>
+          <t>especial</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003978779840848806</v>
+        <v>0.002652519893899204</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>punto</t>
+          <t>querer</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>0.003978779840848806</v>
+        <v>0.002652519893899204</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>especial</t>
+          <t>convertir</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1244,7 +1244,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>querer</t>
+          <t>llevar</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1257,7 +1257,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>convertir</t>
+          <t>recreacion</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1270,7 +1270,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>llevar</t>
+          <t>accesibl</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1283,7 +1283,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>recreacion</t>
+          <t>conocer</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1296,7 +1296,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>accesibl</t>
+          <t>municipio</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1309,7 +1309,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>conocer</t>
+          <t>guanajuato</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1322,7 +1322,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>municipio</t>
+          <t>violencia</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1335,7 +1335,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>guanajuato</t>
+          <t>turista</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1348,7 +1348,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>violencia</t>
+          <t>imagen</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1361,7 +1361,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>turista</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1374,7 +1374,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>imagen</t>
+          <t>delincuencia</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1387,7 +1387,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>realmente</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1400,7 +1400,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>delincuencia</t>
+          <t>impresion</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1413,7 +1413,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>realmente</t>
+          <t>afuera</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1426,7 +1426,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>impresion</t>
+          <t>desconocer</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1439,7 +1439,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>afuera</t>
+          <t>tiempo</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1452,7 +1452,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>desconocer</t>
+          <t>visito</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1465,7 +1465,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tiempo</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1478,7 +1478,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>visito</t>
+          <t>pasar</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1491,7 +1491,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1504,7 +1504,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>pasar</t>
+          <t>foraneo</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1517,7 +1517,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>gustar</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1530,7 +1530,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>foraneo</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1543,7 +1543,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gustar</t>
+          <t>venir</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1556,7 +1556,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>descuidar</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1569,7 +1569,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>venir</t>
+          <t>aparte</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1582,7 +1582,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>descuidar</t>
+          <t>trafico</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1595,7 +1595,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>aparte</t>
+          <t>lindo</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1608,7 +1608,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>trafico</t>
+          <t>bici</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1621,7 +1621,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>lindo</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1634,7 +1634,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>bici</t>
+          <t>paisaje</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1647,7 +1647,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>agradable</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1660,7 +1660,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>paisaje</t>
+          <t>plaza</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1673,7 +1673,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>agradable</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1686,7 +1686,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>plaza</t>
+          <t>rancheria</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1699,7 +1699,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>alrededor</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1712,7 +1712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rancheria</t>
+          <t>faltar</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1725,7 +1725,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>alrededor</t>
+          <t>necesitar</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1738,7 +1738,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>faltar</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1751,7 +1751,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>necesitar</t>
+          <t>encontrar</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1764,7 +1764,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>feria</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1777,7 +1777,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>encontrar</t>
+          <t>local</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1790,7 +1790,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>feria</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1803,7 +1803,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>relativamente</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -1816,7 +1816,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>comodo</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -1829,7 +1829,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>relativamente</t>
+          <t>unico</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -1842,7 +1842,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>comodo</t>
+          <t>promedio</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -1855,7 +1855,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>unico</t>
+          <t>establecimiento</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1868,7 +1868,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>promedio</t>
+          <t>casa</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -1881,7 +1881,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>establecimiento</t>
+          <t>interesante</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1894,7 +1894,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>casa</t>
+          <t>publico</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1907,7 +1907,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>interesante</t>
+          <t>conductor</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -1920,7 +1920,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>publico</t>
+          <t>cruz</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1933,7 +1933,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>conductor</t>
+          <t>peatonal</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1946,7 +1946,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cruz</t>
+          <t>conducir</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1959,7 +1959,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>peatonal</t>
+          <t>escuchar</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1972,7 +1972,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>conducir</t>
+          <t>comodidad</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1985,7 +1985,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>escuchar</t>
+          <t>caro</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1998,7 +1998,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>comodidad</t>
+          <t>deberio</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2011,7 +2011,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>caro</t>
+          <t>comer</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2024,33 +2024,33 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>deberio</t>
+          <t>cultural</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C124" t="n">
-        <v>0.002652519893899204</v>
+        <v>0.001326259946949602</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>comer</t>
+          <t>pequeno</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>0.002652519893899204</v>
+        <v>0.001326259946949602</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>cultural</t>
+          <t>llamativo</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2063,7 +2063,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>pequeno</t>
+          <t>hostil</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2076,7 +2076,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>llamativo</t>
+          <t>recomendario</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2089,7 +2089,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>hostil</t>
+          <t>dejaria</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2102,7 +2102,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>recomendario</t>
+          <t>ultima</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2115,7 +2115,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>dejaria</t>
+          <t>opcion</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2128,7 +2128,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ultima</t>
+          <t>contar</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2141,7 +2141,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>opcion</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2154,7 +2154,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>contar</t>
+          <t>hacer él</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2167,7 +2167,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>crecer</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2180,7 +2180,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>hacer él</t>
+          <t>salmantino</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2193,7 +2193,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>crecer</t>
+          <t>variar</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2206,7 +2206,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>salmantino</t>
+          <t>amabilidad</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2219,7 +2219,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>variar</t>
+          <t>evitar</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2232,7 +2232,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>amabilidad</t>
+          <t>fantasma</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2245,7 +2245,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>evitar</t>
+          <t>tenia</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -2258,7 +2258,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>fantasma</t>
+          <t>perder</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -2271,7 +2271,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tenia</t>
+          <t>oportunidad</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -2284,7 +2284,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>perder</t>
+          <t>laboral</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2297,7 +2297,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>oportunidad</t>
+          <t>estudiantil</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -2310,7 +2310,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>laboral</t>
+          <t>decente</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -2323,7 +2323,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>estudiantil</t>
+          <t>calidad</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2336,7 +2336,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>decente</t>
+          <t>insegura</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -2349,7 +2349,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>calidad</t>
+          <t>aventura</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -2362,7 +2362,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>insegura</t>
+          <t>calir</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -2375,7 +2375,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>aventura</t>
+          <t>caracterizar</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -2388,7 +2388,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>calir</t>
+          <t>resiliente</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -2401,7 +2401,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>caracterizar</t>
+          <t>oler</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -2414,7 +2414,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>resiliente</t>
+          <t>opacado</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -2427,7 +2427,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>oler</t>
+          <t>constante</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -2440,7 +2440,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>opacado</t>
+          <t>ola</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -2453,7 +2453,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>constante</t>
+          <t>causar</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2466,7 +2466,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ola</t>
+          <t>habitante</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2479,7 +2479,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>causar</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2492,7 +2492,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>habitante</t>
+          <t>ambiental</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2505,7 +2505,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>aire</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -2518,7 +2518,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ambiental</t>
+          <t>nivel</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -2531,7 +2531,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>aire</t>
+          <t>quedar</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2544,7 +2544,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nivel</t>
+          <t>lejos</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -2557,7 +2557,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>quedar</t>
+          <t>poner</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2570,7 +2570,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>lejos</t>
+          <t>finta</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2583,7 +2583,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>poner</t>
+          <t>mala</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2596,7 +2596,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>finta</t>
+          <t>experiencia</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2609,7 +2609,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>mala</t>
+          <t>gustariar</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2622,7 +2622,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>experiencia</t>
+          <t>quedar yo</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2635,7 +2635,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>gustariar</t>
+          <t>recomendar</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -2648,7 +2648,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>quedar yo</t>
+          <t>vengar</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -2661,7 +2661,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>recomendar</t>
+          <t>vivirestudiar</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -2674,7 +2674,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>vengar</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -2687,7 +2687,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>vivirestudiar</t>
+          <t>estudio</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -2700,7 +2700,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>compra</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -2713,7 +2713,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>estudio</t>
+          <t>lamentablemente</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -2726,7 +2726,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>compra</t>
+          <t>afectar</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -2739,7 +2739,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>lamentablemente</t>
+          <t>confianza</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -2752,7 +2752,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>afectar</t>
+          <t>turistica</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -2765,7 +2765,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>confianza</t>
+          <t>preguntar</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -2778,7 +2778,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>turistica</t>
+          <t>encuesta</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -2791,7 +2791,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>preguntar</t>
+          <t>evito</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -2804,7 +2804,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>encuesta</t>
+          <t>asisto</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -2817,7 +2817,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>evito</t>
+          <t>concurrido</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -2830,7 +2830,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>asisto</t>
+          <t>disfrutar</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -2843,7 +2843,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>concurrido</t>
+          <t>rato</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -2856,7 +2856,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>disfrutar</t>
+          <t>humo</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -2869,7 +2869,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>rato</t>
+          <t>empresa</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -2882,7 +2882,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>humo</t>
+          <t>pemex</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -2895,7 +2895,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>empresa</t>
+          <t>destino</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -2908,7 +2908,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>pemex</t>
+          <t>valgar</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -2921,7 +2921,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>destino</t>
+          <t>pena</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -2934,7 +2934,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>valgar</t>
+          <t>carino</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -2947,7 +2947,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>pena</t>
+          <t>cerca</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -2960,7 +2960,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>carino</t>
+          <t>disgustar</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -2973,7 +2973,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>cerca</t>
+          <t>colocar</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -2986,7 +2986,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>disgustar</t>
+          <t>sede</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -2999,7 +2999,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>colocar</t>
+          <t>ug</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3012,7 +3012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>sede</t>
+          <t>suciedad</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -3025,7 +3025,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ug</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -3038,7 +3038,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>suciedad</t>
+          <t>asentar él</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -3051,7 +3051,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>arbol</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -3064,7 +3064,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>asentar él</t>
+          <t>atención</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3077,7 +3077,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>arbol</t>
+          <t>bache</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3090,7 +3090,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>atención</t>
+          <t>bandalizado</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -3103,7 +3103,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>bache</t>
+          <t>adaptar</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -3116,7 +3116,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>bandalizado</t>
+          <t>naci</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -3129,7 +3129,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>adaptar</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -3142,7 +3142,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>naci</t>
+          <t>calid</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -3155,7 +3155,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>implementar</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3168,7 +3168,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>calid</t>
+          <t>fuerte</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3181,7 +3181,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>implementar</t>
+          <t>cerrar</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -3194,7 +3194,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>fuerte</t>
+          <t>gestion</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -3207,7 +3207,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>cerrar</t>
+          <t>brutalmente</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -3220,7 +3220,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>gestion</t>
+          <t>abandonado</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -3233,7 +3233,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>brutalmente</t>
+          <t>social</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -3246,7 +3246,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>abandonado</t>
+          <t>estancia</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -3259,7 +3259,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -3272,7 +3272,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>estancia</t>
+          <t>vetir</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -3285,7 +3285,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t xml:space="preserve">dd </t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -3298,7 +3298,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>vetir</t>
+          <t>aburrido</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3311,7 +3311,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">dd </t>
+          <t>apto</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -3324,7 +3324,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>turismo</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -3337,7 +3337,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>apto</t>
+          <t>pequena</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -3350,7 +3350,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>turismo</t>
+          <t>vistas</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -3363,7 +3363,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>pequena</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -3376,7 +3376,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>vistas</t>
+          <t>ruta</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -3389,7 +3389,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>valor</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -3402,7 +3402,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ruta</t>
+          <t>agregado</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -3415,7 +3415,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>cu</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -3428,7 +3428,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>agregado</t>
+          <t>pesimo</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -3441,7 +3441,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>cu</t>
+          <t>sistema</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -3454,7 +3454,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>pesimo</t>
+          <t>horario</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -3467,7 +3467,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sistema</t>
+          <t>vespertino</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -3480,7 +3480,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>horario</t>
+          <t>semana</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -3493,7 +3493,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>vespertino</t>
+          <t>hablar</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -3506,7 +3506,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>semana</t>
+          <t>valorar</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -3519,7 +3519,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>hablar</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -3532,7 +3532,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>valorar</t>
+          <t>increibl</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -3545,7 +3545,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>natural</t>
+          <t>privatizado</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -3558,7 +3558,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>increibl</t>
+          <t>ecoparque</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -3571,7 +3571,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>privatizado</t>
+          <t>seco</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -3584,7 +3584,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ecoparque</t>
+          <t>estanque</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -3597,7 +3597,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>seco</t>
+          <t>lastimo</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -3610,7 +3610,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>estanque</t>
+          <t>interesar</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -3623,7 +3623,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>lastimo</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -3636,7 +3636,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>interesar</t>
+          <t>infraestructura</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -3649,7 +3649,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>viejo</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -3662,7 +3662,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>infraestructura</t>
+          <t>caer</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -3675,7 +3675,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>viejo</t>
+          <t>pedazos</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -3688,7 +3688,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>caer</t>
+          <t>galeria</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -3701,7 +3701,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>pedazos</t>
+          <t>principalmente</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -3714,7 +3714,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>galeria</t>
+          <t>sur</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -3727,7 +3727,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>principalmente</t>
+          <t>pavimento</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -3740,7 +3740,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>sur</t>
+          <t>incluir</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -3753,7 +3753,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>pavimento</t>
+          <t>pertenecer</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -3766,7 +3766,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>incluir</t>
+          <t>elevado</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -3779,7 +3779,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>pertenecer</t>
+          <t>ganar</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -3792,7 +3792,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>elevado</t>
+          <t>sueldo</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -3805,7 +3805,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ganar</t>
+          <t>petrolero</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -3818,7 +3818,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>sueldo</t>
+          <t>noche</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -3831,7 +3831,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>petrolero</t>
+          <t>empezar</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -3844,7 +3844,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>noche</t>
+          <t>invertir</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -3857,7 +3857,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>empezar</t>
+          <t>ocurrir</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -3870,7 +3870,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>invertir</t>
+          <t>basico</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -3883,7 +3883,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ocurrir</t>
+          <t>limpieza</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -3896,7 +3896,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>basico</t>
+          <t>riego</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -3909,7 +3909,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>limpieza</t>
+          <t>ultimamente</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -3922,7 +3922,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>riego</t>
+          <t>percibir</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -3935,7 +3935,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ultimamente</t>
+          <t>nocturno</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -3948,7 +3948,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>percibir</t>
+          <t>terminar</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -3961,7 +3961,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>nocturno</t>
+          <t>toque</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -3974,7 +3974,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>terminar</t>
+          <t>queda</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -3987,7 +3987,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>toque</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -4000,7 +4000,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>queda</t>
+          <t>razón</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -4013,7 +4013,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>pensar</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -4026,7 +4026,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>razón</t>
+          <t>deber</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -4039,7 +4039,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>pensar</t>
+          <t>reconocer</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -4052,7 +4052,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>deber</t>
+          <t>fiesta</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -4065,7 +4065,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>reconocer</t>
+          <t>tianguis</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -4078,7 +4078,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>fiesta</t>
+          <t>producto</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -4091,7 +4091,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>tianguis</t>
+          <t>accesib él</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -4104,7 +4104,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>producto</t>
+          <t>realizar</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -4117,7 +4117,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>accesib él</t>
+          <t>evento</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -4130,7 +4130,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>realizar</t>
+          <t>elote</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -4143,7 +4143,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>nopal</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -4156,7 +4156,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>elote</t>
+          <t>reactivo</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -4169,7 +4169,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>nopal</t>
+          <t>atraer</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -4182,7 +4182,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>reactivo</t>
+          <t>impulsar</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -4195,7 +4195,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>atraer</t>
+          <t>comercio</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -4208,7 +4208,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>impulsar</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -4221,7 +4221,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>comercio</t>
+          <t>importante</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -4234,7 +4234,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>conclusion</t>
+          <t>mejorar</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -4247,7 +4247,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>importante</t>
+          <t>tradición</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -4260,7 +4260,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>mejorar</t>
+          <t>fortalecer</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -4273,7 +4273,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>tradición</t>
+          <t>economia</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -4286,7 +4286,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>fortalecer</t>
+          <t>identidad</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -4299,7 +4299,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>economia</t>
+          <t>arreglo</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -4312,7 +4312,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>identidad</t>
+          <t>provenir</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -4325,7 +4325,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>arreglo</t>
+          <t>recreativo</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -4338,7 +4338,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>provenir</t>
+          <t>excelente</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -4351,7 +4351,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>recreativo</t>
+          <t>genuín</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -4364,7 +4364,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>excelente</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -4377,7 +4377,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>genuín</t>
+          <t>pequén</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -4390,7 +4390,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>cantidad</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -4403,7 +4403,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>pequén</t>
+          <t>deliciós</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -4416,7 +4416,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>cantidad</t>
+          <t>nieve</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -4429,7 +4429,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>deliciós</t>
+          <t>empanada</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -4442,7 +4442,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>nieve</t>
+          <t>antojito</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -4455,7 +4455,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>empanada</t>
+          <t>mexicano</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -4468,7 +4468,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>antojito</t>
+          <t>taco</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -4481,7 +4481,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>mexicano</t>
+          <t>cuestion</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -4494,7 +4494,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>taco</t>
+          <t>art</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -4507,7 +4507,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>cuestion</t>
+          <t>espacio</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -4520,7 +4520,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>art</t>
+          <t>expresion</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -4533,7 +4533,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>espacio</t>
+          <t>artistico</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -4546,7 +4546,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>expresion</t>
+          <t>cine</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -4559,7 +4559,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>artistico</t>
+          <t>historico</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -4572,7 +4572,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>cine</t>
+          <t>seguro</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -4585,7 +4585,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>historico</t>
+          <t>iluminado</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -4598,7 +4598,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>seguro</t>
+          <t>decoracion</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -4611,7 +4611,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>iluminado</t>
+          <t>adicionalmente</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -4624,7 +4624,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>decoracion</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -4637,7 +4637,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>adicionalmente</t>
+          <t>andar</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -4650,7 +4650,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>caminar</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -4663,7 +4663,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>andar</t>
+          <t>colonia</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -4676,7 +4676,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>caminar</t>
+          <t>bellavista</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -4689,7 +4689,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>colonia</t>
+          <t>caminar él</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -4702,7 +4702,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>bellavista</t>
+          <t>muchisir</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -4715,7 +4715,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>caminar él</t>
+          <t>panaderia</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -4728,7 +4728,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>muchisir</t>
+          <t>definitivamente</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -4741,7 +4741,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>panaderia</t>
+          <t>salud</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -4754,7 +4754,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>definitivamente</t>
+          <t>generar</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -4767,7 +4767,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>salud</t>
+          <t>aroma</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -4780,7 +4780,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>generar</t>
+          <t>asqueroso</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -4793,7 +4793,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>aroma</t>
+          <t>paso</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -4806,7 +4806,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>asqueroso</t>
+          <t>saltar</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -4819,7 +4819,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>paso</t>
+          <t>rojo</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -4832,7 +4832,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>saltar</t>
+          <t>musica</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -4845,7 +4845,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>rojo</t>
+          <t>volumen</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -4858,7 +4858,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>musica</t>
+          <t>encender</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -4871,7 +4871,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>volumen</t>
+          <t>direccional</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -4884,7 +4884,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>encender</t>
+          <t>exceso</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -4897,7 +4897,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>direccional</t>
+          <t>velocidad</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -4910,7 +4910,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>exceso</t>
+          <t>personalmente</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -4923,7 +4923,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>velocidad</t>
+          <t>riesgo</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -4936,7 +4936,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>personalmente</t>
+          <t>asaltar</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -4949,7 +4949,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>riesgo</t>
+          <t>violentar</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -4962,7 +4962,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>asaltar</t>
+          <t>ironicamen tú</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -4975,7 +4975,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>violentar</t>
+          <t>inclusivir</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -4988,7 +4988,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ironicamen tú</t>
+          <t>dirio</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -5001,7 +5001,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>inclusivir</t>
+          <t>tranquilo</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -5014,7 +5014,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>dirio</t>
+          <t>entidad</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -5027,7 +5027,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>tranquilo</t>
+          <t>irapuato</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -5040,7 +5040,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>entidad</t>
+          <t>celaya</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -5053,7 +5053,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>irapuato</t>
+          <t>turisticamente</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -5066,7 +5066,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>celaya</t>
+          <t>ventaja</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -5079,7 +5079,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>turisticamente</t>
+          <t>raro</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -5092,7 +5092,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ventaja</t>
+          <t>traslado</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -5105,7 +5105,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>raro</t>
+          <t>sencillo</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -5118,7 +5118,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>traslado</t>
+          <t>rapido</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -5131,7 +5131,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>sencillo</t>
+          <t>recreativa</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -5144,7 +5144,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>rapido</t>
+          <t>opinar</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -5157,7 +5157,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>recreativa</t>
+          <t>respeto</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -5170,7 +5170,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>opinar</t>
+          <t>mandado</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -5183,7 +5183,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>respeto</t>
+          <t>generalmente</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -5196,7 +5196,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>mandado</t>
+          <t>salgo</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -5209,7 +5209,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>generalmente</t>
+          <t>saquenmir</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -5222,7 +5222,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>salgo</t>
+          <t>ayudo</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -5235,7 +5235,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>saquenmir</t>
+          <t>recordar</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -5248,7 +5248,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ayudo</t>
+          <t>mercado</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -5261,7 +5261,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>recordar</t>
+          <t>demasiado</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -5274,7 +5274,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>mercado</t>
+          <t>intentar</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -5287,7 +5287,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>demasiado</t>
+          <t>convivencia</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -5300,7 +5300,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>intentar</t>
+          <t>mayormente</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -5313,7 +5313,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>convivencia</t>
+          <t>destacar</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -5326,7 +5326,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>mayormente</t>
+          <t>motivir</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -5339,7 +5339,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>destacar</t>
+          <t>visualmente</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -5352,7 +5352,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>motivir</t>
+          <t>olor</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -5365,7 +5365,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>visualmente</t>
+          <t>cuidad</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -5378,7 +5378,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>olor</t>
+          <t>chico</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -5391,7 +5391,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>cuidad</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -5404,7 +5404,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>chico</t>
+          <t>souvenirs</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -5417,7 +5417,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ende</t>
+          <t>regreso</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -5430,7 +5430,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>souvenirs</t>
+          <t>diario</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -5443,7 +5443,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>regreso</t>
+          <t>viajar</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -5456,7 +5456,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>diario</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -5469,7 +5469,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>viajar</t>
+          <t>caso</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -5482,7 +5482,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>completo</t>
+          <t>dema</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -5495,7 +5495,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>caso</t>
+          <t>igual</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -5508,7 +5508,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>dema</t>
+          <t>limitar él</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -5521,7 +5521,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>igual</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -5534,7 +5534,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>limitar él</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -5547,7 +5547,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>regresar</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -5560,7 +5560,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>pm</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -5573,7 +5573,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>regresar</t>
+          <t>tocar</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -5586,7 +5586,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>pedir</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -5599,7 +5599,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>tocar</t>
+          <t>uber</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -5612,7 +5612,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>pedir</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -5625,7 +5625,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>uber</t>
+          <t>limitar</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -5638,7 +5638,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>plan</t>
+          <t>relacion</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -5651,7 +5651,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>limitar</t>
+          <t>calidadprecio</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -5664,7 +5664,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>relacion</t>
+          <t>cuidar él</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -5677,7 +5677,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>calidadprecio</t>
+          <t>higiene</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -5690,7 +5690,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>cuidar él</t>
+          <t>deficiente</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -5703,7 +5703,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>higiene</t>
+          <t>ofendar</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -5716,7 +5716,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>deficiente</t>
+          <t>pagu</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -5729,39 +5729,13 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ofendar</t>
+          <t>estudiante</t>
         </is>
       </c>
       <c r="B409" t="n">
         <v>2</v>
       </c>
       <c r="C409" t="n">
-        <v>0.001326259946949602</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>pagu</t>
-        </is>
-      </c>
-      <c r="B410" t="n">
-        <v>2</v>
-      </c>
-      <c r="C410" t="n">
-        <v>0.001326259946949602</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>estudiante</t>
-        </is>
-      </c>
-      <c r="B411" t="n">
-        <v>2</v>
-      </c>
-      <c r="C411" t="n">
         <v>0.001326259946949602</v>
       </c>
     </row>
@@ -5776,7 +5750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C683"/>
+  <dimension ref="A1:C681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5799,33 +5773,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lugar atractivo</t>
+          <t>salamanca ciudad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004310344827586207</v>
+        <v>0.005747126436781609</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>salamanco lugar</t>
+          <t>lugar atractivo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002873563218390805</v>
+        <v>0.004310344827586207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>salamancar ciudad</t>
+          <t>salamanca lugar</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5851,7 +5825,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>salamanco ciudad</t>
+          <t>afuera ciudad</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5864,7 +5838,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>afuera ciudad</t>
+          <t>lugar inseguro</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5877,7 +5851,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lugar inseguro</t>
+          <t>visito universidad</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5890,7 +5864,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>visito universidad</t>
+          <t>lugar lindo</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5903,7 +5877,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lugar lindo</t>
+          <t>salamanca descuidado</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6319,7 +6293,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>amabilidad salamanco</t>
+          <t>amabilidad salamanca</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6332,7 +6306,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>salamanco actualmente</t>
+          <t>salamanca actualmente</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6462,7 +6436,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cultura salamancar</t>
+          <t>cultura salamanca</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -6475,7 +6449,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>salamancar tenia</t>
+          <t>salamanca tenia</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -9738,7 +9712,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>salamanco descuidado</t>
+          <t>descuidado infraestructura</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -9751,7 +9725,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>descuidado infraestructura</t>
+          <t>infraestructura lugar</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -9764,7 +9738,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>infraestructura lugar</t>
+          <t>lugar viejo</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -9777,7 +9751,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>lugar viejo</t>
+          <t>viejo caer</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -9790,7 +9764,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>viejo caer</t>
+          <t>caer pedazos</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -9803,7 +9777,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>caer pedazos</t>
+          <t>pedazos mantenimiento</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -9816,7 +9790,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>pedazos mantenimiento</t>
+          <t>mantenimiento plaza</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -9829,7 +9803,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>mantenimiento plaza</t>
+          <t>plaza galeria</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -9842,7 +9816,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>plaza galeria</t>
+          <t>galeria principalmente</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -9855,7 +9829,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>galeria principalmente</t>
+          <t>principalmente general</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -9868,7 +9842,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>principalmente general</t>
+          <t>general zona</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -9881,7 +9855,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>general zona</t>
+          <t>zona sur</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -9894,7 +9868,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>zona sur</t>
+          <t>sur salamanca</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -9907,7 +9881,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>sur salamanca</t>
+          <t>descuidado calle</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -9920,7 +9894,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>salamanca descuidado</t>
+          <t>calle pavimento</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -9933,7 +9907,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>descuidado calle</t>
+          <t>pavimento actualmente</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -9946,7 +9920,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>calle pavimento</t>
+          <t>actualmente area</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -9959,7 +9933,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>pavimento actualmente</t>
+          <t>verde feo</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -9972,7 +9946,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>actualmente area</t>
+          <t>feo calle</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -9985,7 +9959,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>verde feo</t>
+          <t>calle descuidado</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -9998,7 +9972,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>feo calle</t>
+          <t>descuidado incluir</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -10011,7 +9985,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>calle descuidado</t>
+          <t>incluir rancheria</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -10024,7 +9998,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>descuidado incluir</t>
+          <t>rancheria pertenecer</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -10037,7 +10011,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>incluir rancheria</t>
+          <t>pertenecer salamanca</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -10050,7 +10024,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>rancheria pertenecer</t>
+          <t>salamanca bonito</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -10063,7 +10037,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>pertenecer salamanca</t>
+          <t>bonito turistico</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -10076,7 +10050,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>salamanca bonito</t>
+          <t>turistico mantenimiento</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -10089,7 +10063,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>bonito turistico</t>
+          <t>mantenimiento rancheria</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -10102,7 +10076,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>turistico mantenimiento</t>
+          <t>rancheria precio</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -10115,7 +10089,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>mantenimiento rancheria</t>
+          <t>precio elevado</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -10128,7 +10102,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>rancheria precio</t>
+          <t>elevado salamanca</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -10141,7 +10115,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>precio elevado</t>
+          <t>salamanca ganar</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -10154,7 +10128,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>elevado salamanca</t>
+          <t>ganar sueldo</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -10167,7 +10141,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>salamanca ganar</t>
+          <t>sueldo petrolero</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -10180,7 +10154,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ganar sueldo</t>
+          <t>petrolero ciudad</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -10193,7 +10167,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>sueldo petrolero</t>
+          <t>ciudad alrededor</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -10206,7 +10180,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>petrolero ciudad</t>
+          <t>alrededor variedad</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -10219,7 +10193,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ciudad alrededor</t>
+          <t>variedad aspecto</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -10232,7 +10206,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>alrededor variedad</t>
+          <t>aspecto precio</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -10245,7 +10219,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>variedad aspecto</t>
+          <t>precio accesibl</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -10258,7 +10232,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>aspecto precio</t>
+          <t>feo peligroso</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -10271,7 +10245,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>precio accesibl</t>
+          <t>peligroso salir</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -10284,7 +10258,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>feo peligroso</t>
+          <t>salir noche</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -10297,7 +10271,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>peligroso salir</t>
+          <t>faltar cosa</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -10310,7 +10284,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>salir noche</t>
+          <t>cosa salamanca</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -10323,7 +10297,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>faltar cosa</t>
+          <t>salamanca empezar</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -10336,7 +10310,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>cosa salamanco</t>
+          <t>empezar inseguridad</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -10349,7 +10323,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>salamanco empezar</t>
+          <t>inseguridad ayudar</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -10362,7 +10336,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>empezar inseguridad</t>
+          <t>ayudar general</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -10375,7 +10349,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>inseguridad ayudar</t>
+          <t>sentir salamanca</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -10388,7 +10362,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ayudar general</t>
+          <t>ciudad necesitar</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -10401,7 +10375,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>sentir salamancar</t>
+          <t>necesitar invertir</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -10414,7 +10388,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ciudad necesitar</t>
+          <t>invertir seguridad</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -10427,7 +10401,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>necesitar invertir</t>
+          <t>seguridad ocurrir</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -10440,7 +10414,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>invertir seguridad</t>
+          <t>ocurrir ciudad</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -10453,7 +10427,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>seguridad ocurrir</t>
+          <t>ciudad mexico</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -10466,7 +10440,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ocurrir ciudad</t>
+          <t>mexico considerar</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -10479,7 +10453,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ciudad mexico</t>
+          <t>considerar descuidar</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -10492,7 +10466,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>mexico considerar</t>
+          <t>descuidar ciudad</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -10505,7 +10479,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>considerar descuidar</t>
+          <t>ciudad aspecto</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -10518,7 +10492,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>descuidar ciudad</t>
+          <t>aspecto basico</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -10531,7 +10505,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ciudad aspecto</t>
+          <t>basico limpieza</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -10544,7 +10518,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>aspecto basico</t>
+          <t>limpieza riego</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -10557,7 +10531,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>basico limpieza</t>
+          <t>riego area</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -10570,7 +10544,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>limpieza riego</t>
+          <t>verde mantenimiento</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -10583,7 +10557,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>riego area</t>
+          <t>mantenimiento general</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -10596,7 +10570,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>verde mantenimiento</t>
+          <t>general ultimamente</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -10609,7 +10583,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>mantenimiento general</t>
+          <t>ultimamente percibir</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -10622,7 +10596,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>general ultimamente</t>
+          <t>percibir vida</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -10635,7 +10609,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ultimamente percibir</t>
+          <t>vida nocturno</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -10648,7 +10622,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>percibir vida</t>
+          <t>nocturno terminar</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -10661,7 +10635,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>vida nocturno</t>
+          <t>terminar impresion</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -10674,7 +10648,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>nocturno terminar</t>
+          <t>impresion toque</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -10687,7 +10661,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>terminar impresion</t>
+          <t>toque queda</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -10700,7 +10674,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>impresion toque</t>
+          <t>queda oficial</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -10713,7 +10687,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>toque queda</t>
+          <t>oficial razón</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -10726,7 +10700,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>queda oficial</t>
+          <t>razón pensar</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -10739,7 +10713,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>oficial razón</t>
+          <t>pensar salamanca</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -10752,7 +10726,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>razón pensar</t>
+          <t>salamanca considerar</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -10765,7 +10739,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>pensar salamanca</t>
+          <t>considerar ciudad</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -10778,7 +10752,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>salamanca considerar</t>
+          <t>ciudad turistico</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -10791,7 +10765,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>considerar ciudad</t>
+          <t>turistico deber</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -10804,7 +10778,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ciudad turistico</t>
+          <t>deber reconocer</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -10817,7 +10791,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>turistico deber</t>
+          <t>reconocer aspecto</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -10830,7 +10804,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>deber reconocer</t>
+          <t>aspecto positivo</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -10843,7 +10817,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>reconocer aspecto</t>
+          <t>positivo fiesta</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -10856,7 +10830,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>aspecto positivo</t>
+          <t>fiesta tianguis</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -10869,7 +10843,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>positivo fiesta</t>
+          <t>tianguis ejemplo</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -10882,7 +10856,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>fiesta tianguis</t>
+          <t>ejemplo encontrar</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -10895,7 +10869,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>tianguis ejemplo</t>
+          <t>encontrar producto</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -10908,7 +10882,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ejemplo encontrar</t>
+          <t>producto comida</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -10921,7 +10895,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>encontrar producto</t>
+          <t>comida precio</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -10934,7 +10908,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>producto comida</t>
+          <t>precio accesib él</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -10947,7 +10921,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>comida precio</t>
+          <t>accesib él realizar</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -10960,7 +10934,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>precio accesib él</t>
+          <t>realizar evento</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -10973,7 +10947,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>accesib él realizar</t>
+          <t>evento especial</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -10986,7 +10960,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>realizar evento</t>
+          <t>especial feria</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -10999,7 +10973,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>evento especial</t>
+          <t>feria elote</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -11012,7 +10986,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>especial feria</t>
+          <t>elote feria</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -11025,7 +10999,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>feria elote</t>
+          <t>feria nopal</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -11038,7 +11012,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>elote feria</t>
+          <t>nopal centro</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -11051,7 +11025,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>feria nopal</t>
+          <t>centro ciudad</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -11064,7 +11038,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>nopal centro</t>
+          <t>ciudad reactivo</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -11077,7 +11051,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>centro ciudad</t>
+          <t>reactivo atraer</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -11090,7 +11064,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ciudad reactivo</t>
+          <t>atraer persona</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -11103,7 +11077,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>reactivo atraer</t>
+          <t>persona ayudar</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -11116,7 +11090,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>atraer persona</t>
+          <t>ayudar impulsar</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -11129,7 +11103,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>persona ayudar</t>
+          <t>impulsar comercio</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -11142,7 +11116,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ayudar impulsar</t>
+          <t>comercio local</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -11155,7 +11129,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>impulsar comercio</t>
+          <t>local vida</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -11168,7 +11142,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>comercio local</t>
+          <t>vida lugar</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -11181,7 +11155,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>local vida</t>
+          <t>lugar conclusion</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -11194,7 +11168,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>vida lugar</t>
+          <t>conclusion salamanca</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -11207,7 +11181,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>lugar conclusion</t>
+          <t>salamanca area</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -11220,7 +11194,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>conclusion salamanco</t>
+          <t>area importante</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -11233,7 +11207,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>salamanco area</t>
+          <t>importante mejorar</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -11246,7 +11220,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>area importante</t>
+          <t>mejorar tradición</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -11259,7 +11233,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>importante mejorar</t>
+          <t>tradición actividad</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -11272,7 +11246,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>mejorar tradición</t>
+          <t>actividad fortalecer</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -11285,7 +11259,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>tradición actividad</t>
+          <t>fortalecer economia</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -11298,7 +11272,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>actividad fortalecer</t>
+          <t>economia local</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -11311,7 +11285,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>fortalecer economia</t>
+          <t>local identidad</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -11324,7 +11298,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>economia local</t>
+          <t>ciudad opinion</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -11337,7 +11311,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>local identidad</t>
+          <t>opinion descuidado</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -11350,7 +11324,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ciudad opinion</t>
+          <t>lugar familiar</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -11363,7 +11337,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>opinion descuidado</t>
+          <t>familiar turistico</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -11376,7 +11350,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>lugar familiar</t>
+          <t>turistico faltar</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -11389,7 +11363,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>familiar turistico</t>
+          <t>faltar arreglo</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -11402,7 +11376,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>turistico faltar</t>
+          <t>arreglo paisaje</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -11415,7 +11389,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>faltar arreglo</t>
+          <t>malo salamanca</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -11428,7 +11402,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>arreglo paisaje</t>
+          <t>salamanca provenir</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -11441,7 +11415,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>malo salamanca</t>
+          <t>provenir inseguridad</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -11454,7 +11428,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>salamanca provenir</t>
+          <t>inseguridad falta</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -11467,7 +11441,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>provenir inseguridad</t>
+          <t>falta zona</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -11480,7 +11454,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>inseguridad falta</t>
+          <t>zona recreativo</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -11493,7 +11467,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>falta zona</t>
+          <t>lugar excelente</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -11506,7 +11480,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>zona recreativo</t>
+          <t>excelente turista</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -11519,7 +11493,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>lugar excelente</t>
+          <t>turista variedad</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -11532,7 +11506,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>excelente turista</t>
+          <t>variedad punto</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -11545,7 +11519,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>turista variedad</t>
+          <t>inter lugar</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -11558,7 +11532,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>variedad punto</t>
+          <t>lugar relativamente</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -11571,7 +11545,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>inter lugar</t>
+          <t>relativamente comodo</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -11584,7 +11558,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>lugar relativamente</t>
+          <t>comodo vivir</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -11597,7 +11571,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>relativamente comodo</t>
+          <t>vivir salamanca</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -11610,7 +11584,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>comodo vivir</t>
+          <t>salamanca opinion</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -11623,7 +11597,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>vivir salamanca</t>
+          <t>opinion genuín</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -11636,7 +11610,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>salamanca opinion</t>
+          <t>genuín visitar</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -11649,7 +11623,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>opinion genuín</t>
+          <t>visitar lugar</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -11662,7 +11636,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>genuín visitar</t>
+          <t>lugar realmente</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -11675,7 +11649,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>visitar lugar</t>
+          <t>realmente unico</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -11688,7 +11662,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>lugar realmente</t>
+          <t>unico centro</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -11701,7 +11675,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>realmente unico</t>
+          <t>centro unico</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -11714,7 +11688,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>unico centro</t>
+          <t>unico lugar</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -11727,7 +11701,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>centro unico</t>
+          <t>poder regular</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -11740,7 +11714,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>unico lugar</t>
+          <t>regular ciudad</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -11753,7 +11727,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>poder regular</t>
+          <t>ciudad ciudad</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -11766,7 +11740,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>regular ciudad</t>
+          <t>ciudad promedio</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -11779,7 +11753,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ciudad ciudad</t>
+          <t>promedio guanajuato</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -11792,7 +11766,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>ciudad promedio</t>
+          <t>ciudad relativamente</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -11805,7 +11779,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>promedio guanajuato</t>
+          <t>relativamente pequén</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -11818,7 +11792,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>ciudad relativamente</t>
+          <t>pequén cantidad</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -11831,7 +11805,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>relativamente pequén</t>
+          <t>cantidad establecimiento</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -11844,7 +11818,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>pequén cantidad</t>
+          <t>establecimiento ofrecer</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -11857,7 +11831,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>cantidad establecimiento</t>
+          <t>ofrecer variedad</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -11870,7 +11844,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>establecimiento ofrecer</t>
+          <t>variedad actividad</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -11883,7 +11857,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ofrecer variedad</t>
+          <t>actividad comida</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -11896,7 +11870,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>variedad actividad</t>
+          <t>comida comida</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -11909,7 +11883,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>actividad comida</t>
+          <t>comida salamanca</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -11922,7 +11896,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>comida comida</t>
+          <t>salamanca deliciós</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -11935,7 +11909,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>comida salamanca</t>
+          <t>deliciós nieve</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -11948,7 +11922,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>salamanca deliciós</t>
+          <t>nieve empanada</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -11961,7 +11935,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>deliciós nieve</t>
+          <t>empanada antojito</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -11974,7 +11948,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>nieve empanada</t>
+          <t>antojito mexicano</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -11987,7 +11961,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>empanada antojito</t>
+          <t>mexicano taco</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -12000,7 +11974,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>antojito mexicano</t>
+          <t>taco cuestion</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -12013,7 +11987,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>mexicano taco</t>
+          <t>cuestion variedad</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -12026,7 +12000,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>taco cuestion</t>
+          <t>variedad centro</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -12039,7 +12013,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>cuestion variedad</t>
+          <t>centro art</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -12052,7 +12026,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>variedad centro</t>
+          <t>art casa</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -12065,7 +12039,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>centro art</t>
+          <t>casa cultura</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -12078,7 +12052,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>art casa</t>
+          <t>cultura ofrecer</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -12091,7 +12065,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>casa cultura</t>
+          <t>ofrecer espacio</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -12104,7 +12078,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>cultura ofrecer</t>
+          <t>espacio expresion</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -12117,7 +12091,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>ofrecer espacio</t>
+          <t>expresion artistico</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -12130,7 +12104,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>espacio expresion</t>
+          <t>artistico plaza</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -12143,7 +12117,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>expresion artistico</t>
+          <t>plaza cine</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -12156,7 +12130,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>artistico plaza</t>
+          <t>cine restaurante</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -12169,7 +12143,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>plaza cine</t>
+          <t>restaurante centro</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -12182,7 +12156,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>cine restaurante</t>
+          <t>centro historico</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -12195,7 +12169,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>restaurante centro</t>
+          <t>historico interesante</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -12208,7 +12182,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>centro historico</t>
+          <t>interesante sentir</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -12221,7 +12195,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>historico interesante</t>
+          <t>sentir seguro</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -12234,7 +12208,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>interesante sentir</t>
+          <t>seguro iluminado</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -12247,7 +12221,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>sentir seguro</t>
+          <t>iluminado decoracion</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -12260,7 +12234,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>seguro iluminado</t>
+          <t>decoracion adicionalmente</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -12273,7 +12247,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>iluminado decoracion</t>
+          <t>adicionalmente medio</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -12286,7 +12260,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>decoracion adicionalmente</t>
+          <t>medio transporte</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -12299,7 +12273,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>adicionalmente medio</t>
+          <t>publico comodo</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -12312,7 +12286,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>medio transporte</t>
+          <t>comodo andar</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -12325,7 +12299,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>publico comodo</t>
+          <t>andar bici</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -12338,7 +12312,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>comodo andar</t>
+          <t>bici caminar</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -12351,7 +12325,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>andar bici</t>
+          <t>caminar ejemplo</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -12364,7 +12338,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>bici caminar</t>
+          <t>ejemplo colonia</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -12377,7 +12351,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>caminar ejemplo</t>
+          <t>colonia bellavista</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -12390,7 +12364,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>ejemplo colonia</t>
+          <t>bellavista alrededor</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -12403,7 +12377,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>colonia bellavista</t>
+          <t>alrededor zona</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -12416,7 +12390,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>bellavista alrededor</t>
+          <t>zona bonito</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -12429,7 +12403,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>alrededor zona</t>
+          <t>bonito caminar él</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -12442,7 +12416,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>zona bonito</t>
+          <t>caminar él ofrecer</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -12455,7 +12429,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>bonito caminar él</t>
+          <t>ofrecer muchisir</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -12468,7 +12442,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>caminar él ofrecer</t>
+          <t>muchisir restaurante</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -12481,7 +12455,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ofrecer muchisir</t>
+          <t>restaurante panaderia</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -12494,7 +12468,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>muchisir restaurante</t>
+          <t>panaderia refineria</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -12507,7 +12481,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>restaurante panaderia</t>
+          <t>refineria ciudad</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -12520,7 +12494,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>panaderia refineria</t>
+          <t>ciudad definitivamente</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -12533,7 +12507,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>refineria ciudad</t>
+          <t>definitivamente salud</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -12546,7 +12520,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>ciudad definitivamente</t>
+          <t>salud generar</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -12559,7 +12533,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>definitivamente salud</t>
+          <t>generar aroma</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -12572,7 +12546,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>salud generar</t>
+          <t>aroma asqueroso</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -12585,7 +12559,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>generar aroma</t>
+          <t>asqueroso conductor</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -12598,7 +12572,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>aroma asqueroso</t>
+          <t>conductor paso</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -12611,7 +12585,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>asqueroso conductor</t>
+          <t>paso cruz</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -12624,7 +12598,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>conductor paso</t>
+          <t>peatonal general</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -12637,7 +12611,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>paso cruz</t>
+          <t>general conducir</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -12650,7 +12624,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>peatonal general</t>
+          <t>conducir saltar</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -12663,7 +12637,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>general conducir</t>
+          <t>saltar rojo</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -12676,7 +12650,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>conducir saltar</t>
+          <t>rojo pasar</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -12689,7 +12663,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>saltar rojo</t>
+          <t>pasar musica</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -12702,7 +12676,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>rojo pasar</t>
+          <t>musica alto</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -12715,7 +12689,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>pasar musica</t>
+          <t>alto volumen</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -12728,7 +12702,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>musica alto</t>
+          <t>volumen calle</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -12741,7 +12715,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>alto volumen</t>
+          <t>calle encender</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -12754,7 +12728,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>volumen calle</t>
+          <t>encender direccional</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -12767,7 +12741,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>calle encender</t>
+          <t>direccional conducir</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -12780,7 +12754,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>encender direccional</t>
+          <t>conducir exceso</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -12793,7 +12767,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>direccional conducir</t>
+          <t>exceso velocidad</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -12806,7 +12780,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>conducir exceso</t>
+          <t>velocidad etc</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -12819,7 +12793,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>exceso velocidad</t>
+          <t>etc tema</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -12832,7 +12806,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>velocidad etc</t>
+          <t>tema seguridad</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -12845,7 +12819,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>etc tema</t>
+          <t>seguridad personalmente</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -12858,7 +12832,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>tema seguridad</t>
+          <t>personalmente sentir</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -12871,7 +12845,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>seguridad personalmente</t>
+          <t>sentir riesgo</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -12884,7 +12858,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>personalmente sentir</t>
+          <t>riesgo asaltar</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -12897,7 +12871,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>sentir riesgo</t>
+          <t>asaltar violentar</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -12910,7 +12884,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>riesgo asaltar</t>
+          <t>violentar ironicamen tú</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -12923,7 +12897,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>asaltar violentar</t>
+          <t>ironicamen tú cruz</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -12936,7 +12910,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>violentar ironicamen tú</t>
+          <t>peatonal inclusivir</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -12949,7 +12923,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>ironicamen tú cruz</t>
+          <t>inclusivir dirio</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -12962,7 +12936,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>peatonal inclusivir</t>
+          <t>dirio tranquilo</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -12975,7 +12949,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>inclusivir dirio</t>
+          <t>tranquilo ciudad</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12988,7 +12962,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>dirio tranquilo</t>
+          <t>ciudad entidad</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -13001,7 +12975,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>tranquilo ciudad</t>
+          <t>entidad irapuato</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -13014,7 +12988,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>ciudad entidad</t>
+          <t>irapuato celaya</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -13027,7 +13001,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>entidad irapuato</t>
+          <t>lugar promedio</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -13040,7 +13014,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>irapuato celaya</t>
+          <t>promedio ofrecer</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -13053,7 +13027,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>lugar promedio</t>
+          <t>ofrecer turisticamente</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -13066,7 +13040,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>promedio ofrecer</t>
+          <t>principal ventaja</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -13079,7 +13053,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>ofrecer turisticamente</t>
+          <t>ventaja raro</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -13092,7 +13066,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>principal ventaja</t>
+          <t>raro encontrar</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -13105,7 +13079,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>ventaja raro</t>
+          <t>encontrar trafico</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -13118,7 +13092,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>raro encontrar</t>
+          <t>trafico tiempo</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -13131,7 +13105,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>encontrar trafico</t>
+          <t>tiempo traslado</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -13144,7 +13118,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>trafico tiempo</t>
+          <t>traslado sencillo</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -13157,7 +13131,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>tiempo traslado</t>
+          <t>sencillo rapido</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -13170,7 +13144,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>traslado sencillo</t>
+          <t>rapido falta</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -13183,7 +13157,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>sencillo rapido</t>
+          <t>falta variedad</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -13196,7 +13170,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>rapido falta</t>
+          <t>variedad establecimiento</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -13209,7 +13183,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>falta variedad</t>
+          <t>establecimiento actividad</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -13222,7 +13196,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>variedad establecimiento</t>
+          <t>actividad recreativa</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -13235,7 +13209,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>establecimiento actividad</t>
+          <t>opinar respeto</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -13248,7 +13222,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>actividad recreativa</t>
+          <t>respeto persona</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -13261,7 +13235,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>opinar respeto</t>
+          <t>persona salir</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -13274,7 +13248,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>respeto persona</t>
+          <t>salir casa</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -13287,7 +13261,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>persona salir</t>
+          <t>casa mandado</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -13300,7 +13274,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>salir casa</t>
+          <t>mandado generalmente</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -13313,7 +13287,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>casa mandado</t>
+          <t>generalmente salgo</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -13326,7 +13300,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>mandado generalmente</t>
+          <t>salgo inseguridad</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -13339,7 +13313,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>generalmente salgo</t>
+          <t>saquenmir ayudo</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -13352,7 +13326,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>salgo inseguridad</t>
+          <t>conocer escuchar</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -13365,7 +13339,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>saquenmir ayudo</t>
+          <t>escuchar persona</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -13378,7 +13352,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>conocer escuchar</t>
+          <t>persona vivir</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -13391,7 +13365,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>escuchar persona</t>
+          <t>vivir lugar</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -13404,7 +13378,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>persona vivir</t>
+          <t>lugar contaminado</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -13417,7 +13391,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>vivir lugar</t>
+          <t>contaminado peligroso</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -13430,7 +13404,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>lugar contaminado</t>
+          <t>peligroso recordar</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -13443,7 +13417,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>contaminado peligroso</t>
+          <t>recordar escuchar</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -13456,7 +13430,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>peligroso recordar</t>
+          <t>escuchar cosa</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -13469,7 +13443,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>recordar escuchar</t>
+          <t>cosa positivo</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -13482,7 +13456,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>escuchar cosa</t>
+          <t>positivo lugar</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -13495,7 +13469,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>cosa positivo</t>
+          <t>lugar mercado</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -13508,7 +13482,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>positivo lugar</t>
+          <t>lugar punto</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -13521,7 +13495,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>lugar mercado</t>
+          <t>inter demasiado</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -13534,7 +13508,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>lugar punto</t>
+          <t>demasiado contaminacion</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -13547,7 +13521,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>inter demasiado</t>
+          <t>contaminacion peligroso</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -13560,7 +13534,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>demasiado contaminacion</t>
+          <t>peligroso interesante</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -13573,7 +13547,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>contaminacion peligroso</t>
+          <t>interesante poder</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -13586,7 +13560,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>peligroso interesante</t>
+          <t>punto malo</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -13599,7 +13573,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>interesante poder</t>
+          <t>malo malo</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -13612,7 +13586,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>punto malo</t>
+          <t>malo intentar</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -13625,7 +13599,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>malo malo</t>
+          <t>intentar cosa</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -13638,7 +13612,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>malo intentar</t>
+          <t>cosa comodidad</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -13651,7 +13625,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>intentar cosa</t>
+          <t>comodidad convivencia</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -13664,7 +13638,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>cosa comodidad</t>
+          <t>convivencia mayormente</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -13677,7 +13651,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>comodidad convivencia</t>
+          <t>general ciudad</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -13690,7 +13664,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>convivencia mayormente</t>
+          <t>ciudad destacar</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -13703,7 +13677,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>general ciudad</t>
+          <t>destacar atractivo</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -13716,7 +13690,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>ciudad destacar</t>
+          <t>atractivo turistico</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -13729,7 +13703,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>destacar atractivo</t>
+          <t>turistico motivir</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -13742,7 +13716,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>atractivo turistico</t>
+          <t>motivir gente</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -13755,7 +13729,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>turistico motivir</t>
+          <t>gente querer</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -13768,7 +13742,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>motivir gente</t>
+          <t>querer visitar</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -13781,7 +13755,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>gente querer</t>
+          <t>visitar ciudad</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -13794,7 +13768,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>querer visitar</t>
+          <t>ciudad visualmente</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -13807,7 +13781,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>visitar ciudad</t>
+          <t>visualmente bonito</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -13820,7 +13794,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>ciudad visualmente</t>
+          <t>bonito mayoria</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -13833,7 +13807,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>visualmente bonito</t>
+          <t>mayoria olor</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -13846,7 +13820,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>bonito mayoria</t>
+          <t>olor agradable</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -13859,7 +13833,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>mayoria olor</t>
+          <t>cuidad chico</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -13872,7 +13846,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>olor agradable</t>
+          <t>chico ende</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -13885,7 +13859,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>cuidad chico</t>
+          <t>ende variedad</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -13898,7 +13872,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>chico ende</t>
+          <t>variedad comida</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -13911,7 +13885,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>ende variedad</t>
+          <t>comida lugar</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -13924,7 +13898,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>variedad comida</t>
+          <t>lugar souvenirs</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -13937,7 +13911,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>comida lugar</t>
+          <t>souvenirs atracción</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -13950,7 +13924,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>lugar souvenirs</t>
+          <t>atracción aparte</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -13963,7 +13937,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>souvenirs atracción</t>
+          <t>aparte sentir</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -13976,7 +13950,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>atracción aparte</t>
+          <t>sentir tanto</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -13989,7 +13963,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>aparte sentir</t>
+          <t>tanto cultura</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -14002,7 +13976,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>sentir tanto</t>
+          <t>cultura tema</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -14015,7 +13989,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>tanto cultura</t>
+          <t>tema inseguridad</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -14028,7 +14002,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>cultura tema</t>
+          <t>foraneo venir</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -14041,7 +14015,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>tema inseguridad</t>
+          <t>venir regreso</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -14054,7 +14028,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>foraneo venir</t>
+          <t>regreso diario</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -14067,7 +14041,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>venir regreso</t>
+          <t>diario ver</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -14080,7 +14054,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>regreso diario</t>
+          <t>ver viajar</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -14093,7 +14067,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>diario ver</t>
+          <t>viajar opinion</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -14106,7 +14080,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>ver viajar</t>
+          <t>opinion completo</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -14119,7 +14093,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>viajar opinion</t>
+          <t>inseguro transporte</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -14132,7 +14106,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>opinion completo</t>
+          <t>transporte caro</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -14145,7 +14119,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>inseguro transporte</t>
+          <t>caro comida</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -14158,7 +14132,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>transporte caro</t>
+          <t>transporte ejemplo</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -14171,7 +14145,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>caro comida</t>
+          <t>ejemplo caso</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -14184,7 +14158,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>transporte ejemplo</t>
+          <t>caso desconocer</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -14197,7 +14171,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>ejemplo caso</t>
+          <t>desconocer dema</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -14210,7 +14184,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>caso desconocer</t>
+          <t>dema igual</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -14223,7 +14197,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>desconocer dema</t>
+          <t>igual deberio</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -14236,7 +14210,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>dema igual</t>
+          <t>deberio limitar él</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -14249,7 +14223,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>igual deberio</t>
+          <t>limitar él 7</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14262,7 +14236,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>deberio limitar él</t>
+          <t>7 pm</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -14275,7 +14249,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>limitar él 7</t>
+          <t>pm necesitar</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -14288,7 +14262,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>7 pm</t>
+          <t>necesitar regresar</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -14301,7 +14275,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>pm necesitar</t>
+          <t>regresar 730</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -14314,7 +14288,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>necesitar regresar</t>
+          <t>730 tocar</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -14327,7 +14301,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>regresar 730</t>
+          <t>tocar pedir</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -14340,7 +14314,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>730 tocar</t>
+          <t>pedir uber</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -14353,7 +14327,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>tocar pedir</t>
+          <t>uber caro</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -14366,7 +14340,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>pedir uber</t>
+          <t>caro considerar</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -14379,7 +14353,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>uber caro</t>
+          <t>considerar cosa</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -14392,7 +14366,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>caro considerar</t>
+          <t>cosa comer</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -14405,7 +14379,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>considerar cosa</t>
+          <t>comer plan</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -14418,7 +14392,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>cosa comer</t>
+          <t>plan limitar</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -14431,7 +14405,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>comer plan</t>
+          <t>limitar salir</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -14444,7 +14418,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>plan limitar</t>
+          <t>salir comer</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -14457,7 +14431,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>limitar salir</t>
+          <t>comer comida</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -14470,7 +14444,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>salir comer</t>
+          <t>comida relacion</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -14483,7 +14457,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>comer comida</t>
+          <t>relacion calidadprecio</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -14496,7 +14470,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>comida relacion</t>
+          <t>calidadprecio deberio</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14509,7 +14483,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>relacion calidadprecio</t>
+          <t>deberio cuidar él</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -14522,7 +14496,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>calidadprecio deberio</t>
+          <t>cuidar él higiene</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -14535,7 +14509,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>deberio cuidar él</t>
+          <t>higiene comodidad</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -14548,7 +14522,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>cuidar él higiene</t>
+          <t>comodidad transporte</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -14561,7 +14535,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>higiene comodidad</t>
+          <t>publico deficiente</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -14574,7 +14548,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>comodidad transporte</t>
+          <t>deficiente conductor</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -14587,7 +14561,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>publico deficiente</t>
+          <t>conductor ofendar</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -14600,7 +14574,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>deficiente conductor</t>
+          <t>ofendar pagu</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -14613,7 +14587,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>conductor ofendar</t>
+          <t>pagu precio</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -14626,39 +14600,13 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>ofendar pagu</t>
+          <t>precio estudiante</t>
         </is>
       </c>
       <c r="B681" t="n">
         <v>2</v>
       </c>
       <c r="C681" t="n">
-        <v>0.001436781609195402</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>pagu precio</t>
-        </is>
-      </c>
-      <c r="B682" t="n">
-        <v>2</v>
-      </c>
-      <c r="C682" t="n">
-        <v>0.001436781609195402</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>precio estudiante</t>
-        </is>
-      </c>
-      <c r="B683" t="n">
-        <v>2</v>
-      </c>
-      <c r="C683" t="n">
         <v>0.001436781609195402</v>
       </c>
     </row>
@@ -14761,7 +14709,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>salamanco lugar hostil</t>
+          <t>salamanca lugar hostil</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -14891,7 +14839,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>salamancar ciudad gobierno</t>
+          <t>salamanca ciudad gobierno</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -15008,7 +14956,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>variar amabilidad salamanco</t>
+          <t>variar amabilidad salamanca</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -15021,7 +14969,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>amabilidad salamanco actualmente</t>
+          <t>amabilidad salamanca actualmente</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -15034,7 +14982,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>salamanco actualmente lugar</t>
+          <t>salamanca actualmente lugar</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -15151,7 +15099,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gastronomia cultura salamancar</t>
+          <t>gastronomia cultura salamanca</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -15164,7 +15112,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cultura salamancar tenia</t>
+          <t>cultura salamanca tenia</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -15177,7 +15125,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>salamancar tenia perder</t>
+          <t>salamanca tenia perder</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -15346,7 +15294,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>salamanco lugar lugar</t>
+          <t>salamanca lugar lugar</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -16061,7 +16009,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>salamanco ciudad visitar</t>
+          <t>salamanca ciudad visitar</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -18245,7 +18193,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>salamanco descuidado infraestructura</t>
+          <t>salamanca descuidado infraestructura</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -18817,7 +18765,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>faltar cosa salamanco</t>
+          <t>faltar cosa salamanca</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -18830,7 +18778,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>cosa salamanco empezar</t>
+          <t>cosa salamanca empezar</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -18843,7 +18791,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>salamanco empezar inseguridad</t>
+          <t>salamanca empezar inseguridad</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -18882,7 +18830,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>sentir salamancar ciudad</t>
+          <t>sentir salamanca ciudad</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -18895,7 +18843,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>salamancar ciudad necesitar</t>
+          <t>salamanca ciudad necesitar</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -19714,7 +19662,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>lugar conclusion salamanco</t>
+          <t>lugar conclusion salamanca</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -19727,7 +19675,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>conclusion salamanco area</t>
+          <t>conclusion salamanca area</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -19740,7 +19688,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>salamanco area importante</t>
+          <t>salamanca area importante</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -19844,7 +19792,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>salamanco ciudad opinion</t>
+          <t>salamanca ciudad opinion</t>
         </is>
       </c>
       <c r="B398" t="n">
